--- a/AACSB programme info.xlsx
+++ b/AACSB programme info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29518"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yorksj-my.sharepoint.com/personal/h_may_yorksj_ac_uk/Documents/AACSB/Eligibility application/Programme data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41FE52F6-4E48-4E85-8B87-56228E7BC6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{766D58A5-6A81-41F9-93CF-59DF6F277AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Progs not in scope" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Export!$A$1:$AR$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Export!$A$1:$AR$122</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -279,7 +279,7 @@
     <t>COM</t>
   </si>
   <si>
-    <t>BA (Hons) Global Business Management (Level 6 Direct Entry)</t>
+    <t>BA (Hons) Global Business Management</t>
   </si>
   <si>
     <r>
@@ -1579,7 +1579,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -1672,6 +1672,12 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1829,7 +1835,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2142,6 +2148,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2687,16 +2696,16 @@
     <col min="4" max="4" width="18.140625" style="118" customWidth="1"/>
     <col min="5" max="5" width="55.42578125" style="29" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="10.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="23.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="24" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="24" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="23.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="24" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="24" style="118" customWidth="1"/>
     <col min="14" max="35" width="9.140625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="36" max="36" width="11.140625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="8.7109375" style="17" collapsed="1"/>
+    <col min="37" max="37" width="8.7109375" style="17" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="38" max="38" width="53.28515625" style="3" customWidth="1"/>
     <col min="39" max="43" width="39.42578125" style="3" customWidth="1"/>
     <col min="44" max="44" width="39.42578125" style="12" customWidth="1"/>
@@ -2995,7 +3004,7 @@
       <c r="D4" s="116">
         <v>3</v>
       </c>
-      <c r="E4" s="106" t="s">
+      <c r="E4" s="125" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -3630,25 +3639,25 @@
       <c r="AK11" s="20">
         <v>331</v>
       </c>
-      <c r="AL11" s="125" t="s">
+      <c r="AL11" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="AM11" s="125" t="s">
+      <c r="AM11" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="AN11" s="125" t="s">
+      <c r="AN11" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="AO11" s="125" t="s">
+      <c r="AO11" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="AP11" s="126" t="s">
+      <c r="AP11" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="AQ11" s="127" t="s">
+      <c r="AQ11" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="AR11" s="126" t="s">
+      <c r="AR11" s="127" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3724,13 +3733,13 @@
       <c r="AK12" s="20">
         <v>70</v>
       </c>
-      <c r="AL12" s="125"/>
-      <c r="AM12" s="125"/>
-      <c r="AN12" s="125"/>
-      <c r="AO12" s="125"/>
-      <c r="AP12" s="126"/>
-      <c r="AQ12" s="126"/>
-      <c r="AR12" s="126"/>
+      <c r="AL12" s="126"/>
+      <c r="AM12" s="126"/>
+      <c r="AN12" s="126"/>
+      <c r="AO12" s="126"/>
+      <c r="AP12" s="127"/>
+      <c r="AQ12" s="127"/>
+      <c r="AR12" s="127"/>
     </row>
     <row r="13" spans="1:45" ht="146.25" customHeight="1">
       <c r="A13" s="3" t="s">
@@ -3898,7 +3907,7 @@
       <c r="B15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="156" t="s">
+      <c r="C15" s="157" t="s">
         <v>74</v>
       </c>
       <c r="D15" s="115">
@@ -3969,25 +3978,25 @@
       <c r="AK15" s="62">
         <v>515</v>
       </c>
-      <c r="AL15" s="144" t="s">
+      <c r="AL15" s="145" t="s">
         <v>76</v>
       </c>
-      <c r="AM15" s="144" t="s">
+      <c r="AM15" s="145" t="s">
         <v>77</v>
       </c>
-      <c r="AN15" s="144" t="s">
+      <c r="AN15" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="AO15" s="144" t="s">
+      <c r="AO15" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="AP15" s="144" t="s">
+      <c r="AP15" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="AQ15" s="144" t="s">
+      <c r="AQ15" s="145" t="s">
         <v>81</v>
       </c>
-      <c r="AR15" s="139" t="s">
+      <c r="AR15" s="140" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3998,7 +4007,7 @@
       <c r="B16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="157"/>
+      <c r="C16" s="158"/>
       <c r="D16" s="120">
         <v>10</v>
       </c>
@@ -4063,13 +4072,13 @@
       <c r="AK16" s="49">
         <v>115</v>
       </c>
-      <c r="AL16" s="146"/>
-      <c r="AM16" s="146"/>
-      <c r="AN16" s="155"/>
-      <c r="AO16" s="155"/>
-      <c r="AP16" s="155"/>
-      <c r="AQ16" s="146"/>
-      <c r="AR16" s="148"/>
+      <c r="AL16" s="147"/>
+      <c r="AM16" s="147"/>
+      <c r="AN16" s="156"/>
+      <c r="AO16" s="156"/>
+      <c r="AP16" s="156"/>
+      <c r="AQ16" s="147"/>
+      <c r="AR16" s="149"/>
     </row>
     <row r="17" spans="1:272" ht="14.45" customHeight="1">
       <c r="A17" s="3" t="s">
@@ -4382,25 +4391,25 @@
       <c r="AK21" s="62">
         <v>2</v>
       </c>
-      <c r="AL21" s="144" t="s">
+      <c r="AL21" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="AM21" s="144" t="s">
+      <c r="AM21" s="145" t="s">
         <v>93</v>
       </c>
-      <c r="AN21" s="144" t="s">
+      <c r="AN21" s="145" t="s">
         <v>94</v>
       </c>
-      <c r="AO21" s="144" t="s">
+      <c r="AO21" s="145" t="s">
         <v>95</v>
       </c>
-      <c r="AP21" s="144" t="s">
+      <c r="AP21" s="145" t="s">
         <v>96</v>
       </c>
-      <c r="AQ21" s="144" t="s">
+      <c r="AQ21" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="AR21" s="139" t="s">
+      <c r="AR21" s="140" t="s">
         <v>98</v>
       </c>
     </row>
@@ -4464,13 +4473,13 @@
       <c r="AK22" s="49">
         <v>15</v>
       </c>
-      <c r="AL22" s="146"/>
-      <c r="AM22" s="146"/>
-      <c r="AN22" s="146"/>
-      <c r="AO22" s="146"/>
-      <c r="AP22" s="146"/>
-      <c r="AQ22" s="158"/>
-      <c r="AR22" s="148"/>
+      <c r="AL22" s="147"/>
+      <c r="AM22" s="147"/>
+      <c r="AN22" s="147"/>
+      <c r="AO22" s="147"/>
+      <c r="AP22" s="147"/>
+      <c r="AQ22" s="159"/>
+      <c r="AR22" s="149"/>
     </row>
     <row r="23" spans="1:272">
       <c r="A23" s="3" t="s">
@@ -4633,25 +4642,25 @@
       <c r="AK24" s="62">
         <v>92</v>
       </c>
-      <c r="AL24" s="139" t="s">
+      <c r="AL24" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="AM24" s="139" t="s">
+      <c r="AM24" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="AN24" s="139" t="s">
+      <c r="AN24" s="140" t="s">
         <v>108</v>
       </c>
-      <c r="AO24" s="139" t="s">
+      <c r="AO24" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="AP24" s="139" t="s">
+      <c r="AP24" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="AQ24" s="139" t="s">
+      <c r="AQ24" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="AR24" s="139" t="s">
+      <c r="AR24" s="140" t="s">
         <v>112</v>
       </c>
       <c r="AS24" s="34"/>
@@ -4953,13 +4962,13 @@
       <c r="AK25" s="19">
         <v>25</v>
       </c>
-      <c r="AL25" s="140"/>
-      <c r="AM25" s="140"/>
-      <c r="AN25" s="140"/>
-      <c r="AO25" s="140"/>
-      <c r="AP25" s="140"/>
-      <c r="AQ25" s="140"/>
-      <c r="AR25" s="140"/>
+      <c r="AL25" s="141"/>
+      <c r="AM25" s="141"/>
+      <c r="AN25" s="141"/>
+      <c r="AO25" s="141"/>
+      <c r="AP25" s="141"/>
+      <c r="AQ25" s="141"/>
+      <c r="AR25" s="141"/>
     </row>
     <row r="26" spans="1:272" s="1" customFormat="1" ht="76.5" customHeight="1">
       <c r="A26" s="36" t="s">
@@ -5029,13 +5038,13 @@
       <c r="AK26" s="49">
         <v>19</v>
       </c>
-      <c r="AL26" s="141"/>
-      <c r="AM26" s="141"/>
-      <c r="AN26" s="141"/>
-      <c r="AO26" s="141"/>
-      <c r="AP26" s="141"/>
-      <c r="AQ26" s="141"/>
-      <c r="AR26" s="141"/>
+      <c r="AL26" s="142"/>
+      <c r="AM26" s="142"/>
+      <c r="AN26" s="142"/>
+      <c r="AO26" s="142"/>
+      <c r="AP26" s="142"/>
+      <c r="AQ26" s="142"/>
+      <c r="AR26" s="142"/>
       <c r="AS26" s="37"/>
       <c r="AT26" s="37"/>
       <c r="AU26" s="37"/>
@@ -5520,7 +5529,7 @@
       <c r="AK30" s="56">
         <v>203</v>
       </c>
-      <c r="AL30" s="142" t="s">
+      <c r="AL30" s="143" t="s">
         <v>121</v>
       </c>
       <c r="AM30" s="82" t="s">
@@ -5616,7 +5625,7 @@
       <c r="AK31" s="20">
         <v>30</v>
       </c>
-      <c r="AL31" s="143"/>
+      <c r="AL31" s="144"/>
       <c r="AM31" s="87"/>
       <c r="AN31" s="87"/>
       <c r="AO31" s="87"/>
@@ -7106,25 +7115,25 @@
       <c r="AK53" s="41">
         <v>49</v>
       </c>
-      <c r="AL53" s="134" t="s">
+      <c r="AL53" s="135" t="s">
         <v>175</v>
       </c>
-      <c r="AM53" s="134" t="s">
+      <c r="AM53" s="135" t="s">
         <v>176</v>
       </c>
-      <c r="AN53" s="134" t="s">
+      <c r="AN53" s="135" t="s">
         <v>177</v>
       </c>
-      <c r="AO53" s="134" t="s">
+      <c r="AO53" s="135" t="s">
         <v>178</v>
       </c>
-      <c r="AP53" s="134" t="s">
+      <c r="AP53" s="135" t="s">
         <v>179</v>
       </c>
-      <c r="AQ53" s="134" t="s">
+      <c r="AQ53" s="135" t="s">
         <v>180</v>
       </c>
-      <c r="AR53" s="137" t="s">
+      <c r="AR53" s="138" t="s">
         <v>181</v>
       </c>
       <c r="AS53" s="34"/>
@@ -7424,13 +7433,13 @@
       <c r="AK54" s="44">
         <v>10</v>
       </c>
-      <c r="AL54" s="135"/>
-      <c r="AM54" s="136"/>
-      <c r="AN54" s="135"/>
-      <c r="AO54" s="135"/>
-      <c r="AP54" s="135"/>
-      <c r="AQ54" s="135"/>
-      <c r="AR54" s="138"/>
+      <c r="AL54" s="136"/>
+      <c r="AM54" s="137"/>
+      <c r="AN54" s="136"/>
+      <c r="AO54" s="136"/>
+      <c r="AP54" s="136"/>
+      <c r="AQ54" s="136"/>
+      <c r="AR54" s="139"/>
     </row>
     <row r="55" spans="1:272">
       <c r="A55" s="35" t="s">
@@ -7496,13 +7505,13 @@
       <c r="AK55" s="44">
         <v>1</v>
       </c>
-      <c r="AL55" s="135"/>
-      <c r="AM55" s="136"/>
-      <c r="AN55" s="135"/>
-      <c r="AO55" s="135"/>
-      <c r="AP55" s="135"/>
-      <c r="AQ55" s="135"/>
-      <c r="AR55" s="138"/>
+      <c r="AL55" s="136"/>
+      <c r="AM55" s="137"/>
+      <c r="AN55" s="136"/>
+      <c r="AO55" s="136"/>
+      <c r="AP55" s="136"/>
+      <c r="AQ55" s="136"/>
+      <c r="AR55" s="139"/>
     </row>
     <row r="56" spans="1:272" s="46" customFormat="1" ht="14.45" customHeight="1">
       <c r="A56" s="36" t="s">
@@ -7585,7 +7594,7 @@
       <c r="B57" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C57" s="149" t="s">
+      <c r="C57" s="150" t="s">
         <v>185</v>
       </c>
       <c r="D57" s="115">
@@ -7660,25 +7669,25 @@
       <c r="AK57" s="62">
         <v>159</v>
       </c>
-      <c r="AL57" s="144" t="s">
+      <c r="AL57" s="145" t="s">
         <v>187</v>
       </c>
-      <c r="AM57" s="144" t="s">
+      <c r="AM57" s="145" t="s">
         <v>188</v>
       </c>
-      <c r="AN57" s="144" t="s">
+      <c r="AN57" s="145" t="s">
         <v>189</v>
       </c>
-      <c r="AO57" s="144" t="s">
+      <c r="AO57" s="145" t="s">
         <v>190</v>
       </c>
-      <c r="AP57" s="152" t="s">
+      <c r="AP57" s="153" t="s">
         <v>191</v>
       </c>
-      <c r="AQ57" s="144" t="s">
+      <c r="AQ57" s="145" t="s">
         <v>192</v>
       </c>
-      <c r="AR57" s="139" t="s">
+      <c r="AR57" s="140" t="s">
         <v>193</v>
       </c>
     </row>
@@ -7689,7 +7698,7 @@
       <c r="B58" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="150"/>
+      <c r="C58" s="151"/>
       <c r="D58" s="116">
         <v>26</v>
       </c>
@@ -7750,13 +7759,13 @@
       <c r="AK58" s="20">
         <v>18</v>
       </c>
-      <c r="AL58" s="145"/>
-      <c r="AM58" s="145"/>
-      <c r="AN58" s="145"/>
-      <c r="AO58" s="145"/>
-      <c r="AP58" s="153"/>
-      <c r="AQ58" s="145"/>
-      <c r="AR58" s="147"/>
+      <c r="AL58" s="146"/>
+      <c r="AM58" s="146"/>
+      <c r="AN58" s="146"/>
+      <c r="AO58" s="146"/>
+      <c r="AP58" s="154"/>
+      <c r="AQ58" s="146"/>
+      <c r="AR58" s="148"/>
     </row>
     <row r="59" spans="1:272" s="46" customFormat="1" ht="393.95" customHeight="1">
       <c r="A59" s="72" t="s">
@@ -7765,7 +7774,7 @@
       <c r="B59" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="151"/>
+      <c r="C59" s="152"/>
       <c r="D59" s="120">
         <v>26</v>
       </c>
@@ -7820,13 +7829,13 @@
       <c r="AK59" s="49">
         <v>7</v>
       </c>
-      <c r="AL59" s="146"/>
-      <c r="AM59" s="146"/>
-      <c r="AN59" s="146"/>
-      <c r="AO59" s="146"/>
-      <c r="AP59" s="154"/>
-      <c r="AQ59" s="146"/>
-      <c r="AR59" s="148"/>
+      <c r="AL59" s="147"/>
+      <c r="AM59" s="147"/>
+      <c r="AN59" s="147"/>
+      <c r="AO59" s="147"/>
+      <c r="AP59" s="155"/>
+      <c r="AQ59" s="147"/>
+      <c r="AR59" s="149"/>
     </row>
     <row r="60" spans="1:272" s="31" customFormat="1" ht="409.5" customHeight="1">
       <c r="A60" s="30" t="s">
@@ -7910,25 +7919,25 @@
       <c r="AK60" s="62">
         <v>72</v>
       </c>
-      <c r="AL60" s="128" t="s">
+      <c r="AL60" s="129" t="s">
         <v>197</v>
       </c>
-      <c r="AM60" s="128" t="s">
+      <c r="AM60" s="129" t="s">
         <v>198</v>
       </c>
-      <c r="AN60" s="128" t="s">
+      <c r="AN60" s="129" t="s">
         <v>199</v>
       </c>
       <c r="AO60" s="111" t="s">
         <v>200</v>
       </c>
-      <c r="AP60" s="128" t="s">
+      <c r="AP60" s="129" t="s">
         <v>201</v>
       </c>
-      <c r="AQ60" s="128" t="s">
+      <c r="AQ60" s="129" t="s">
         <v>202</v>
       </c>
-      <c r="AR60" s="131" t="s">
+      <c r="AR60" s="132" t="s">
         <v>203</v>
       </c>
       <c r="AS60" s="68"/>
@@ -8234,13 +8243,13 @@
       <c r="AK61" s="20">
         <v>12</v>
       </c>
-      <c r="AL61" s="129"/>
-      <c r="AM61" s="129"/>
-      <c r="AN61" s="129"/>
+      <c r="AL61" s="130"/>
+      <c r="AM61" s="130"/>
+      <c r="AN61" s="130"/>
       <c r="AO61" s="112"/>
-      <c r="AP61" s="129"/>
-      <c r="AQ61" s="129"/>
-      <c r="AR61" s="132"/>
+      <c r="AP61" s="130"/>
+      <c r="AQ61" s="130"/>
+      <c r="AR61" s="133"/>
     </row>
     <row r="62" spans="1:272" s="1" customFormat="1" ht="60.95" customHeight="1">
       <c r="A62" s="36" t="s">
@@ -8314,13 +8323,13 @@
       <c r="AK62" s="49">
         <v>11</v>
       </c>
-      <c r="AL62" s="130"/>
-      <c r="AM62" s="130"/>
-      <c r="AN62" s="130"/>
+      <c r="AL62" s="131"/>
+      <c r="AM62" s="131"/>
+      <c r="AN62" s="131"/>
       <c r="AO62" s="102"/>
-      <c r="AP62" s="130"/>
-      <c r="AQ62" s="130"/>
-      <c r="AR62" s="133"/>
+      <c r="AP62" s="131"/>
+      <c r="AQ62" s="131"/>
+      <c r="AR62" s="134"/>
       <c r="AS62" s="37"/>
       <c r="AT62" s="37"/>
       <c r="AU62" s="37"/>
@@ -9036,25 +9045,25 @@
       <c r="AK69" s="62">
         <v>30</v>
       </c>
-      <c r="AL69" s="144" t="s">
+      <c r="AL69" s="145" t="s">
         <v>217</v>
       </c>
-      <c r="AM69" s="144" t="s">
+      <c r="AM69" s="145" t="s">
         <v>218</v>
       </c>
-      <c r="AN69" s="144" t="s">
+      <c r="AN69" s="145" t="s">
         <v>219</v>
       </c>
-      <c r="AO69" s="144" t="s">
+      <c r="AO69" s="145" t="s">
         <v>220</v>
       </c>
-      <c r="AP69" s="144" t="s">
+      <c r="AP69" s="145" t="s">
         <v>221</v>
       </c>
-      <c r="AQ69" s="144" t="s">
+      <c r="AQ69" s="145" t="s">
         <v>222</v>
       </c>
-      <c r="AR69" s="139" t="s">
+      <c r="AR69" s="140" t="s">
         <v>223</v>
       </c>
     </row>
@@ -9121,13 +9130,13 @@
       <c r="AK70" s="20">
         <v>15</v>
       </c>
-      <c r="AL70" s="145"/>
-      <c r="AM70" s="145"/>
-      <c r="AN70" s="145"/>
-      <c r="AO70" s="145"/>
-      <c r="AP70" s="145"/>
-      <c r="AQ70" s="145"/>
-      <c r="AR70" s="147"/>
+      <c r="AL70" s="146"/>
+      <c r="AM70" s="146"/>
+      <c r="AN70" s="146"/>
+      <c r="AO70" s="146"/>
+      <c r="AP70" s="146"/>
+      <c r="AQ70" s="146"/>
+      <c r="AR70" s="148"/>
     </row>
     <row r="71" spans="1:44" s="11" customFormat="1" ht="14.45" customHeight="1">
       <c r="A71" s="71" t="s">
@@ -9203,13 +9212,13 @@
       <c r="AK71" s="20">
         <v>477</v>
       </c>
-      <c r="AL71" s="145"/>
-      <c r="AM71" s="145"/>
-      <c r="AN71" s="145"/>
-      <c r="AO71" s="145"/>
-      <c r="AP71" s="145"/>
-      <c r="AQ71" s="145"/>
-      <c r="AR71" s="147"/>
+      <c r="AL71" s="146"/>
+      <c r="AM71" s="146"/>
+      <c r="AN71" s="146"/>
+      <c r="AO71" s="146"/>
+      <c r="AP71" s="146"/>
+      <c r="AQ71" s="146"/>
+      <c r="AR71" s="148"/>
     </row>
     <row r="72" spans="1:44" s="11" customFormat="1" ht="14.45" customHeight="1">
       <c r="A72" s="71" t="s">
@@ -9285,13 +9294,13 @@
       <c r="AK72" s="20">
         <v>47</v>
       </c>
-      <c r="AL72" s="145"/>
-      <c r="AM72" s="145"/>
-      <c r="AN72" s="145"/>
-      <c r="AO72" s="145"/>
-      <c r="AP72" s="145"/>
-      <c r="AQ72" s="145"/>
-      <c r="AR72" s="147"/>
+      <c r="AL72" s="146"/>
+      <c r="AM72" s="146"/>
+      <c r="AN72" s="146"/>
+      <c r="AO72" s="146"/>
+      <c r="AP72" s="146"/>
+      <c r="AQ72" s="146"/>
+      <c r="AR72" s="148"/>
     </row>
     <row r="73" spans="1:44" s="46" customFormat="1" ht="204.6" customHeight="1">
       <c r="A73" s="72" t="s">
@@ -9357,13 +9366,13 @@
       <c r="AK73" s="49">
         <v>22</v>
       </c>
-      <c r="AL73" s="146"/>
-      <c r="AM73" s="146"/>
-      <c r="AN73" s="146"/>
-      <c r="AO73" s="146"/>
-      <c r="AP73" s="146"/>
-      <c r="AQ73" s="146"/>
-      <c r="AR73" s="148"/>
+      <c r="AL73" s="147"/>
+      <c r="AM73" s="147"/>
+      <c r="AN73" s="147"/>
+      <c r="AO73" s="147"/>
+      <c r="AP73" s="147"/>
+      <c r="AQ73" s="147"/>
+      <c r="AR73" s="149"/>
     </row>
     <row r="74" spans="1:44" ht="14.45" customHeight="1">
       <c r="A74" s="3" t="s">
@@ -10538,25 +10547,25 @@
       <c r="AK91" s="20">
         <v>187</v>
       </c>
-      <c r="AL91" s="127" t="s">
+      <c r="AL91" s="128" t="s">
         <v>248</v>
       </c>
-      <c r="AM91" s="125" t="s">
+      <c r="AM91" s="126" t="s">
         <v>249</v>
       </c>
-      <c r="AN91" s="160" t="s">
+      <c r="AN91" s="161" t="s">
         <v>250</v>
       </c>
-      <c r="AO91" s="162" t="s">
+      <c r="AO91" s="163" t="s">
         <v>251</v>
       </c>
-      <c r="AP91" s="160" t="s">
+      <c r="AP91" s="161" t="s">
         <v>252</v>
       </c>
-      <c r="AQ91" s="160" t="s">
+      <c r="AQ91" s="161" t="s">
         <v>253</v>
       </c>
-      <c r="AR91" s="159" t="s">
+      <c r="AR91" s="160" t="s">
         <v>254</v>
       </c>
     </row>
@@ -10622,13 +10631,13 @@
       <c r="AK92" s="20">
         <v>13</v>
       </c>
-      <c r="AL92" s="127"/>
-      <c r="AM92" s="145"/>
-      <c r="AN92" s="153"/>
-      <c r="AO92" s="153"/>
-      <c r="AP92" s="160"/>
-      <c r="AQ92" s="160"/>
-      <c r="AR92" s="159"/>
+      <c r="AL92" s="128"/>
+      <c r="AM92" s="146"/>
+      <c r="AN92" s="154"/>
+      <c r="AO92" s="154"/>
+      <c r="AP92" s="161"/>
+      <c r="AQ92" s="161"/>
+      <c r="AR92" s="160"/>
     </row>
     <row r="93" spans="1:44" s="11" customFormat="1" ht="98.25" customHeight="1">
       <c r="A93" s="24" t="s">
@@ -10703,25 +10712,25 @@
       <c r="AK93" s="20">
         <v>263</v>
       </c>
-      <c r="AL93" s="160" t="s">
+      <c r="AL93" s="161" t="s">
         <v>257</v>
       </c>
-      <c r="AM93" s="160" t="s">
+      <c r="AM93" s="161" t="s">
         <v>258</v>
       </c>
-      <c r="AN93" s="160" t="s">
+      <c r="AN93" s="161" t="s">
         <v>259</v>
       </c>
-      <c r="AO93" s="160" t="s">
+      <c r="AO93" s="161" t="s">
         <v>260</v>
       </c>
-      <c r="AP93" s="153" t="s">
+      <c r="AP93" s="154" t="s">
         <v>261</v>
       </c>
-      <c r="AQ93" s="160" t="s">
+      <c r="AQ93" s="161" t="s">
         <v>262</v>
       </c>
-      <c r="AR93" s="159" t="s">
+      <c r="AR93" s="160" t="s">
         <v>263</v>
       </c>
     </row>
@@ -10784,13 +10793,13 @@
       <c r="AK94" s="20">
         <v>8</v>
       </c>
-      <c r="AL94" s="153"/>
-      <c r="AM94" s="153"/>
-      <c r="AN94" s="153"/>
-      <c r="AO94" s="153"/>
-      <c r="AP94" s="153"/>
-      <c r="AQ94" s="153"/>
-      <c r="AR94" s="163"/>
+      <c r="AL94" s="154"/>
+      <c r="AM94" s="154"/>
+      <c r="AN94" s="154"/>
+      <c r="AO94" s="154"/>
+      <c r="AP94" s="154"/>
+      <c r="AQ94" s="154"/>
+      <c r="AR94" s="164"/>
     </row>
     <row r="95" spans="1:44" ht="14.45" customHeight="1">
       <c r="A95" s="3" t="s">
@@ -10986,22 +10995,22 @@
       <c r="AK97" s="20">
         <v>53</v>
       </c>
-      <c r="AL97" s="162" t="s">
+      <c r="AL97" s="163" t="s">
         <v>268</v>
       </c>
-      <c r="AM97" s="160" t="s">
+      <c r="AM97" s="161" t="s">
         <v>269</v>
       </c>
-      <c r="AN97" s="160" t="s">
+      <c r="AN97" s="161" t="s">
         <v>270</v>
       </c>
-      <c r="AO97" s="160" t="s">
+      <c r="AO97" s="161" t="s">
         <v>271</v>
       </c>
-      <c r="AP97" s="160" t="s">
+      <c r="AP97" s="161" t="s">
         <v>272</v>
       </c>
-      <c r="AQ97" s="160" t="s">
+      <c r="AQ97" s="161" t="s">
         <v>273</v>
       </c>
       <c r="AR97" s="108" t="s">
@@ -11070,12 +11079,12 @@
       <c r="AK98" s="20">
         <v>1</v>
       </c>
-      <c r="AL98" s="162"/>
-      <c r="AM98" s="160"/>
-      <c r="AN98" s="160"/>
-      <c r="AO98" s="160"/>
-      <c r="AP98" s="160"/>
-      <c r="AQ98" s="160"/>
+      <c r="AL98" s="163"/>
+      <c r="AM98" s="161"/>
+      <c r="AN98" s="161"/>
+      <c r="AO98" s="161"/>
+      <c r="AP98" s="161"/>
+      <c r="AQ98" s="161"/>
       <c r="AR98" s="27"/>
     </row>
     <row r="99" spans="1:44" ht="130.5" customHeight="1">
@@ -11376,25 +11385,25 @@
       <c r="AK102" s="20">
         <v>30</v>
       </c>
-      <c r="AL102" s="160" t="s">
+      <c r="AL102" s="161" t="s">
         <v>287</v>
       </c>
-      <c r="AM102" s="160" t="s">
+      <c r="AM102" s="161" t="s">
         <v>288</v>
       </c>
-      <c r="AN102" s="160" t="s">
+      <c r="AN102" s="161" t="s">
         <v>289</v>
       </c>
-      <c r="AO102" s="160" t="s">
+      <c r="AO102" s="161" t="s">
         <v>290</v>
       </c>
-      <c r="AP102" s="161" t="s">
+      <c r="AP102" s="162" t="s">
         <v>291</v>
       </c>
-      <c r="AQ102" s="160" t="s">
+      <c r="AQ102" s="161" t="s">
         <v>292</v>
       </c>
-      <c r="AR102" s="159" t="s">
+      <c r="AR102" s="160" t="s">
         <v>293</v>
       </c>
     </row>
@@ -11460,13 +11469,13 @@
       <c r="AK103" s="20">
         <v>2</v>
       </c>
-      <c r="AL103" s="160"/>
-      <c r="AM103" s="160"/>
-      <c r="AN103" s="160"/>
-      <c r="AO103" s="160"/>
-      <c r="AP103" s="161"/>
-      <c r="AQ103" s="160"/>
-      <c r="AR103" s="159"/>
+      <c r="AL103" s="161"/>
+      <c r="AM103" s="161"/>
+      <c r="AN103" s="161"/>
+      <c r="AO103" s="161"/>
+      <c r="AP103" s="162"/>
+      <c r="AQ103" s="161"/>
+      <c r="AR103" s="160"/>
     </row>
     <row r="104" spans="1:44" ht="14.45" customHeight="1">
       <c r="A104" s="3" t="s">
